--- a/extenbooks/S1509_extenbook.xlsx
+++ b/extenbooks/S1509_extenbook.xlsx
@@ -2881,7 +2881,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -3726,11 +3726,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3753,64 +3753,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1509</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1509_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1509_DPR.md", "epr": "Technical/docs/series/S1509_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1509_load.py", "processor": "Technical/code/P02_processors/P02_S1509_construct.py", "validator": "Technical/code/V03_validators/V03_S1509_validate.py", "processed": "Technical/data/processed/S1509.parquet", "chopped_csv": "Technical/chopped/S1509.csv", "extenbook_xlsx": "Technical/extenbooks/S1509_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1509_extenbook.xlsx
+++ b/extenbooks/S1509_extenbook.xlsx
@@ -2828,7 +2828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A106"/>
+  <dimension ref="A1:A108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2867,7 +2867,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -3006,45 +3006,45 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units |</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1509-A, S1509-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| **S1509-lambda** | 46 rows (38 unique countries, some have multiple sub-period entries) | Ramamurthy (2014) ch.3, reproduced in `Appendix15_WorldInflationDataByCountry.xlsx` sheet `Ramamurthy2013` | Rate (percent) |</t>
+          <t>| Subseries | Coverage | Source | Native units |</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| **S1509-pi** | 46 rows | same xlsx | Rate (percent) |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| **S1509-episode** | 46 rows | Acute / Chronic / Control classification | categorical |</t>
+          <t>| **S1509-lambda** | 46 rows (38 unique countries, some have multiple sub-period entries) | Ramamurthy (2014) ch.3, reproduced in `Appendix15_WorldInflationDataByCountry.xlsx` sheet `Ramamurthy2013` | Rate (percent) |</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>| **S1509-pi** | 46 rows | same xlsx | Rate (percent) |</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Underlying IFS sources: line 32 (Domestic Claims) and line 64 (CPI). Modern equivalents: `DCORP_N_DC` and `PCPI_IX` via `_imf_ifs_resolver`.</t>
+          <t>| **S1509-episode** | 46 rows | Acute / Chronic / Control classification | categorical |</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>Underlying IFS sources: line 32 (Domestic Claims) and line 64 (CPI). Modern equivalents: `DCORP_N_DC` and `PCPI_IX` via `_imf_ifs_resolver`.</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>`direct` cross-sectional: verbatim load of the chopped table. Romania appears twice in different sub-periods (an artifact preserved in the data; Phase 4 noted Shaikh's narrative collapses these into a "39-country" count, but the effective unique country count is 38 with Romania having two sub-period observations).</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>`direct` cross-sectional: verbatim load of the chopped table. Romania appears twice in different sub-periods (an artifact preserved in the data; the data-adequacy review noted Shaikh's narrative collapses these into a "39-country" count, but the effective unique country count is 38 with Romania having two sub-period observations).</t>
         </is>
       </c>
     </row>
@@ -3084,24 +3084,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>- **Book**: 1988-2011 (cross-section of country-period averages)</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>- **Extension**: **not_applicable_cross_sectional**</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Extension**: **not_applicable_cross_sectional**</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rate (percent), same convention as S1508.</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>Rate (percent), same convention as S1508.</t>
         </is>
       </c>
     </row>
@@ -3131,38 +3131,38 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1. **Cross_sectional**: no time series extension.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2. **Romania de-duplication**: 39 countries in Shaikh's footnote, but Romania has two sub-period rows (1991-1994 Acute episode + 1998-2002 Chronic episode). The "38 unique countries" count refers to country-level uniqueness; the dataset has 46 country-episode rows total per the chopped table (8 additional sub-period splits for other countries).</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3. **Ramamurthy 2014 citation**: NSSR PhD dissertation under Shaikh; ProQuest citation deferred to Phase 6+ (Q6 of Phase 4).</t>
+          <t>1. **Cross_sectional**: no time series extension.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4. **IMF IFS code remap** documented in `_imf_ifs_resolver` for any modern re-pull.</t>
+          <t>2. **Romania de-duplication**: 39 countries in Shaikh's footnote, but Romania has two sub-period rows (1991-1994 Acute episode + 1998-2002 Chronic episode). The "38 unique countries" count refers to country-level uniqueness; the dataset has 46 country-episode rows total per the chopped table (8 additional sub-period splits for other countries).</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3. **Ramamurthy 2014 citation**: NSSR PhD dissertation under Shaikh; ProQuest citation deferred to a later enrichment pass.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>4. **IMF IFS code remap** documented in `_imf_ifs_resolver` for any modern re-pull.</t>
         </is>
       </c>
     </row>
@@ -3172,24 +3172,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S082`</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figure 15.13; Appendix 15.1 p. 897</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>- **Predecessor-build ID**: `S082`</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figure 15.13; Appendix 15.1 p. 897</t>
         </is>
       </c>
     </row>
@@ -3199,82 +3199,82 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>- **Tolerance**: +/- 0.5% per cell against the chopped table.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>- **Expected MAE**: zero (verbatim load).</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4">
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>- **Expected mean absolute error (MAE)**: zero (verbatim load).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4">
         <f>== EPR: S1509_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t># S1509 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-    </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>**Series**: S1509 — Ramamurthy 38-country (46-episode) cross-section, 1988-2011</t>
+          <t># S1509 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>**Construction classification**: `direct` (`cross_sectional` content type)</t>
+          <t>**Series**: S1509 — Ramamurthy 38-country (46-episode) cross-section, 1988-2011</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>**Extension method**: **not_applicable_cross_sectional**</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Construction classification**: `direct` (`cross_sectional` content type)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Extension method**: **not_applicable_cross_sectional**</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>## 1. Why no time-series extension</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S1509 is `cross_sectional`. The 46 country-episode rows are a historical snapshot of inflationary regimes from 1988-2011. There is no "extending it to 2025".</t>
+          <t>## 1. Why no time-series extension</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>## 2. Optional modern re-pull (Phase 6+ enrichment)</t>
+          <t>S1509 is `cross_sectional`. The 46 country-episode rows are a historical snapshot of inflationary regimes from 1988-2011. There is no "extending it to 2025".</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A modern reconstruction would fetch, per country-episode, IMF MFS_DC `DCORP_N_DC` and CPI `PCPI_IX` for the episode period, then compute period-average gDC and pi:</t>
+          <t>## 2. Optional modern re-pull (later enrichment pass)</t>
         </is>
       </c>
     </row>
@@ -3324,52 +3324,52 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>```python</t>
+          <t>A modern reconstruction would fetch, per country-episode, IMF MFS_DC `DCORP_N_DC` and CPI `PCPI_IX` for the episode period, then compute period-average gDC and pi:</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>from loaders._imf_ifs_resolver import resolve_ifs_line, fetch_ifs_series</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>modern_credit = resolve_ifs_line(32)  # "DCORP_N_DC"</t>
+          <t>```python</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>modern_cpi    = resolve_ifs_line(64)  # "PCPI_IX"</t>
+          <t>from loaders._imf_ifs_resolver import resolve_ifs_line, fetch_ifs_series</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t># loop over countries + episode windows ...</t>
+          <t>modern_credit = resolve_ifs_line(32)  # "DCORP_N_DC"</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>modern_cpi    = resolve_ifs_line(64)  # "PCPI_IX"</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t># loop over countries + episode windows ...</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pre-2001 IMF SDMX 3.0 USA data is missing; the same gap likely applies to many of the Eastern European countries with 1988-1995 episodes. Therefore the modern re-pull is best treated as a Phase 6+ enrichment, never as primary extension.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>## 3. No proxies</t>
+          <t>Pre-2001 IMF SDMX (Statistical Data and Metadata eXchange) 3.0 USA data is missing; the same gap likely applies to many of the Eastern European countries with 1988-1995 episodes. Therefore the modern re-pull is best treated as a later enrichment pass, never as primary extension.</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ramamurthy's IFS-derived values are the canonical replication target. The modern resolver lookup is a code remap, not a concept proxy.</t>
+          <t>## 3. No proxies</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>## 4. No synthetic data</t>
+          <t>Ramamurthy's IFS-derived values are the canonical replication target. The modern resolver lookup is a code remap, not a concept proxy.</t>
         </is>
       </c>
     </row>
@@ -3408,6 +3408,16 @@
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
+        <is>
+          <t>## 4. No synthetic data</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>Verbatim load. Romania de-duplication is a documented count interpretation, not a data substitution.</t>
         </is>
@@ -3582,11 +3592,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3628,7 +3638,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3706,12 +3716,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>independent_anchors</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"status": "GREEN", "any_red": false, "anchors": {"status": "GREEN", "sid": "S1509", "n_anchors": 1, "n_red": 0, "n_green": 1, "n_na": 0, "anchors": [{"anchor_id": "S1509_panel_cardinality", "anchor_type": "derived_statistic", "subseries_id": "S1509-lambda", "source_description": "Ramamurthy (2014, ch.3) panel structure independently asserted in S1509 MHR SS1/SS4 + DPR SS3: 46 country-episode rows (= 38 unique countries; Romania appears as TWO episodes: Acute 1991-94, Chronic 1998-02). Structural anchor independent of the numeric cell round-trip; the printed numeric cells are circular (same xlsx V03 reads) and the book 'ten times higher' claim is qualitative, so no independent numeric value anchor exists.", "status": "GREEN", "expected": 46.0, "actual": 46.0, "abs_pct_diff": 0.0, "tolerance_pct": 1.0, "detail": "n=46"}]}, "splice": {"status": "NA", "sid": "S1509", "detail": "no extension / no book+extension ranges"}, "plausibility": {"status": "NA", "sid": "S1509", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:14:08.338123+00:00</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-02T06:19:56.869688+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1509_extenbook.xlsx
+++ b/extenbooks/S1509_extenbook.xlsx
@@ -3733,7 +3733,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T06:19:56.869688+00:00</t>
+          <t>2026-07-11T03:44:23.525963+00:00</t>
         </is>
       </c>
     </row>
@@ -3748,11 +3748,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3775,6 +3775,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RAMAMURTHY_2014_CH3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful direct replication of book figure 15.13 - Ramamurthy's updated 38-country / 46-episode cross-section (Romania de-duplicated from the 39-entry footnote) extending Harberger to 1988-2011. Cross-sectional country panel; the single year label (2011) is correct and the COVERAGE_START prescreen flag is an index-axis false positive. Hyperinflation magnitudes verified (Armenia pi 23.12 = 2,312%) consistent with the book's note that the upper range is ten times higher than figure 15.12.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1509_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1509_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
